--- a/measurements/31/Filled_2D_sections/sagittal/week31_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/31/Filled_2D_sections/sagittal/week31_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AG28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,102 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +596,70 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.049375371802499</v>
+        <v>2687.074829931973</v>
       </c>
       <c r="D2" t="n">
-        <v>14.33547305479282</v>
+        <v>279.8830453554789</v>
       </c>
       <c r="E2" t="n">
-        <v>11.99688161873236</v>
+        <v>234.2248316038223</v>
       </c>
       <c r="F2" t="n">
         <v>1.194933276028072</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4310587283755807</v>
+        <v>0.4310587283755808</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5963224085365854</v>
+        <v>1.244419642857143</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8978658536585367</v>
+        <v>17.52976190476191</v>
       </c>
       <c r="K2" t="n">
-        <v>0.747094131097561</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>6.109250992063494</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>17.52976190476191</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>11.64248511904762</v>
+      </c>
+      <c r="V2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.244419642857143</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.041294642857143</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.870814732142857</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>7.168619869125521</v>
+      <c r="AG2" s="2" t="n">
+        <v>2732.528344671201</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +670,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.098750743604997</v>
+        <v>2705.895691609977</v>
       </c>
       <c r="D3" t="n">
-        <v>14.51875887556774</v>
+        <v>283.4614828087035</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95055246643904</v>
+        <v>233.3203100590479</v>
       </c>
       <c r="F3" t="n">
         <v>1.214902734943932</v>
@@ -572,24 +689,51 @@
         <v>0.4231874754375918</v>
       </c>
       <c r="H3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.333705357142857</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17.54650297619047</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.795865221088434</v>
+      </c>
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.6685403963414634</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8987233231707318</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.7836318597560976</v>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="n">
+        <v>17.54650297619047</v>
+      </c>
+      <c r="N3" t="n">
+        <v>13.05245535714286</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.333705357142857</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.218005952380952</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.994419642857143</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>13.35773100896579</v>
+      <c r="AG3" s="2" t="n">
+        <v>260.7937958893322</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +744,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.14098750743605</v>
+        <v>2721.995464852608</v>
       </c>
       <c r="D4" t="n">
-        <v>14.82327793865669</v>
+        <v>289.4068549928211</v>
       </c>
       <c r="E4" t="n">
-        <v>11.99933291935339</v>
+        <v>234.2726903302329</v>
       </c>
       <c r="F4" t="n">
         <v>1.235341834273857</v>
@@ -619,24 +763,51 @@
         <v>0.4083942641036674</v>
       </c>
       <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.34672619047619</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17.46465773809524</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.867249503968253</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.7575266768292683</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.89453125</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.8260289634146342</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="n">
+        <v>17.46465773809524</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14.78980654761905</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.34672619047619</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.591889880952381</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.237258184523809</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>11.85499462150946</v>
+      <c r="AG4" s="2" t="n">
+        <v>231.4546568961371</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +818,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.199286139202856</v>
+        <v>2744.21768707483</v>
       </c>
       <c r="D5" t="n">
-        <v>14.82327792702652</v>
+        <v>289.4068547657558</v>
       </c>
       <c r="E5" t="n">
-        <v>11.99933298041181</v>
+        <v>234.2726915223258</v>
       </c>
       <c r="F5" t="n">
         <v>1.235341827018604</v>
@@ -666,24 +837,51 @@
         <v>0.4117283732037707</v>
       </c>
       <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.515997023809524</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16.88430059523809</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.393880208333334</v>
+      </c>
+      <c r="L5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.7301829268292683</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.8648056402439025</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.7974942835365855</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="n">
+        <v>16.88430059523809</v>
+      </c>
+      <c r="N5" t="n">
+        <v>14.25595238095238</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.515997023809524</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.151041666666667</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.001798115079365</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
-        <v>1.126472941651919</v>
+      <c r="AG5" s="2" t="n">
+        <v>1.12647294165192</v>
       </c>
     </row>
     <row r="6">
@@ -694,42 +892,72 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.310826888756693</v>
+        <v>2786.734693877551</v>
       </c>
       <c r="D6" t="n">
-        <v>13.8717610167294</v>
+        <v>270.8296198504311</v>
       </c>
       <c r="E6" t="n">
-        <v>12.26344095206842</v>
+        <v>239.4290852546692</v>
       </c>
       <c r="F6" t="n">
         <v>1.13114753607467</v>
       </c>
       <c r="G6" t="n">
-        <v>0.477433807130936</v>
+        <v>0.4774338071309361</v>
       </c>
       <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.26860119047619</v>
+      </c>
+      <c r="J6" t="n">
+        <v>15.57477678571428</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.280133928571429</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.7977324695121951</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.7977324695121951</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.7977324695121951</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="n">
+        <v>15.57477678571428</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8.774181547619047</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.542410714285714</v>
+      </c>
+      <c r="V6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.26860119047619</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.994791666666667</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.987138605442177</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AG6" s="2" t="n">
         <v>0.5091507094526133</v>
       </c>
     </row>
@@ -741,43 +969,70 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.366151100535396</v>
+        <v>2807.8231292517</v>
       </c>
       <c r="D7" t="n">
-        <v>13.70521398288448</v>
+        <v>267.5779872848874</v>
       </c>
       <c r="E7" t="n">
-        <v>12.38957681016224</v>
+        <v>241.8917377222152</v>
       </c>
       <c r="F7" t="n">
         <v>1.106189032352026</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4928092442950134</v>
+        <v>0.4928092442950132</v>
       </c>
       <c r="H7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.729910714285714</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15.06696428571428</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.57072585978836</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.7717225609756098</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.7717225609756098</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.7717225609756098</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="n">
+        <v>15.06696428571428</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9.345238095238095</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.729910714285714</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.066220238095238</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.389190051020408</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.6</v>
+      <c r="AG7" s="2" t="n">
+        <v>8.1</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1043,70 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7.375966686496134</v>
+        <v>2811.56462585034</v>
       </c>
       <c r="D8" t="n">
-        <v>13.73970702799355</v>
+        <v>268.2514229274931</v>
       </c>
       <c r="E8" t="n">
-        <v>12.30038526290801</v>
+        <v>240.1503789424896</v>
       </c>
       <c r="F8" t="n">
         <v>1.117014364535869</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4909913780759548</v>
+        <v>0.4909913780759547</v>
       </c>
       <c r="H8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.428571428571428</v>
+      </c>
+      <c r="J8" t="n">
+        <v>14.98697916666667</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.576306216931217</v>
+      </c>
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.767625762195122</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.767625762195122</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.767625762195122</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="n">
+        <v>14.98697916666667</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>9.484747023809524</v>
+      </c>
+      <c r="V8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.428571428571428</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.523065476190476</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.387861394557823</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.7305044778963414</v>
+      <c r="AG8" s="2" t="n">
+        <v>1.626395089285714</v>
       </c>
     </row>
     <row r="9">
@@ -835,17 +1117,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7.365258774538965</v>
+        <v>2807.482993197279</v>
       </c>
       <c r="D9" t="n">
-        <v>13.87421234351833</v>
+        <v>270.8774790877387</v>
       </c>
       <c r="E9" t="n">
-        <v>12.23385058961264</v>
+        <v>238.8513686543419</v>
       </c>
       <c r="F9" t="n">
         <v>1.134083847263794</v>
@@ -854,24 +1136,54 @@
         <v>0.4808185341248805</v>
       </c>
       <c r="H9" t="n">
+        <v>9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.428571428571428</v>
+      </c>
+      <c r="J9" t="n">
+        <v>14.72842261904762</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.785052910052909</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.7543826219512195</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.7543826219512195</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.7543826219512195</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="n">
+        <v>14.72842261904762</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>9.555431547619047</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.518229166666666</v>
+      </c>
+      <c r="V9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.428571428571428</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.881324404761905</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.377232142857143</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.8309236852134146</v>
+      <c r="AG9" s="2" t="n">
+        <v>11.32114955357143</v>
       </c>
     </row>
     <row r="10">
@@ -882,34 +1194,70 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.530041641879833</v>
+        <v>2870.294784580499</v>
       </c>
       <c r="D10" t="n">
-        <v>12.99269689583197</v>
+        <v>253.6669393948146</v>
       </c>
       <c r="E10" t="n">
-        <v>11.98403009263481</v>
+        <v>233.9739208562033</v>
       </c>
       <c r="F10" t="n">
         <v>1.084167579303483</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5605426055841048</v>
+        <v>0.560542605584105</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.783854166666667</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.166666666666666</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.195498511904762</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9.166666666666666</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7.981770833333333</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.783854166666667</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.863467261904762</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.735925099206349</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.7807140815548781</v>
+      <c r="AG10" s="2" t="n">
+        <v>4.81569283529384</v>
       </c>
     </row>
     <row r="11">
@@ -920,26 +1268,73 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.467876264128495</v>
+        <v>2846.598639455782</v>
       </c>
       <c r="D11" t="n">
-        <v>13.35191446978872</v>
+        <v>260.6802348863511</v>
       </c>
       <c r="E11" t="n">
-        <v>11.98403010717252</v>
+        <v>233.973921140035</v>
       </c>
       <c r="F11" t="n">
         <v>1.114142266865426</v>
       </c>
       <c r="G11" t="n">
-        <v>0.526404864795544</v>
+        <v>0.5264048647955442</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.036830357142857</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.94345238095238</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.261946097883597</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8.94345238095238</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7.829241071428571</v>
+      </c>
+      <c r="R11" t="n">
+        <v>4.877232142857142</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.036830357142857</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.296130952380952</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.784598214285714</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="12">
@@ -950,26 +1345,73 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.399464604402142</v>
+        <v>2820.521541950113</v>
       </c>
       <c r="D12" t="n">
-        <v>13.16516195564735</v>
+        <v>257.0341143721626</v>
       </c>
       <c r="E12" t="n">
-        <v>11.89483855119566</v>
+        <v>232.2325621900104</v>
       </c>
       <c r="F12" t="n">
         <v>1.10679618718524</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5364852040702229</v>
+        <v>0.5364852040702228</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.923363095238095</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8.809523809523808</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.646344866071428</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>8.809523809523808</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.619047619047619</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4.747023809523809</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.923363095238095</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.764880952380952</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.199032738095238</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="n">
+        <v>16.22279575892857</v>
       </c>
     </row>
     <row r="13">
@@ -980,26 +1422,73 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7.305770374776919</v>
+        <v>2784.807256235827</v>
       </c>
       <c r="D13" t="n">
-        <v>12.91534146157707</v>
+        <v>252.1566666307903</v>
       </c>
       <c r="E13" t="n">
-        <v>11.96729129988973</v>
+        <v>233.6471158549899</v>
       </c>
       <c r="F13" t="n">
         <v>1.079220112382163</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5503818408667602</v>
+        <v>0.5503818408667603</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.618303571428571</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8.288690476190476</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.557989211309524</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8.288690476190476</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6.25790550595238</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.618303571428571</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.389136904761905</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.858072916666667</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="n">
+        <v>14.0327380952381</v>
       </c>
     </row>
     <row r="14">
@@ -1010,26 +1499,73 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7.244794765020822</v>
+        <v>2761.56462585034</v>
       </c>
       <c r="D14" t="n">
-        <v>12.82023179531097</v>
+        <v>250.2997636227381</v>
       </c>
       <c r="E14" t="n">
-        <v>11.93871633890199</v>
+        <v>233.0892237595149</v>
       </c>
       <c r="F14" t="n">
         <v>1.073836703326018</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5539163648302072</v>
+        <v>0.5539163648302071</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.432291666666667</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7.619047619047619</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.290261243386243</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.52938988095238</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7.619047619047619</v>
+      </c>
+      <c r="U14" t="n">
+        <v>6.18071056547619</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.432291666666667</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.902529761904762</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.777901785714286</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -1040,26 +1576,73 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.156454491374182</v>
+        <v>2727.891156462585</v>
       </c>
       <c r="D15" t="n">
-        <v>12.82614991432283</v>
+        <v>250.4153078510648</v>
       </c>
       <c r="E15" t="n">
-        <v>11.84115537782995</v>
+        <v>231.1844621385847</v>
       </c>
       <c r="F15" t="n">
         <v>1.083183988813885</v>
       </c>
       <c r="G15" t="n">
-        <v>0.546657303120672</v>
+        <v>0.5466573031206721</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.73735119047619</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7.619047619047619</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.796549479166666</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4.427083333333333</v>
+      </c>
+      <c r="T15" t="n">
+        <v>7.619047619047619</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5.988467261904761</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.627232142857143</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.06547619047619</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.73735119047619</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="n">
+        <v>9.465215773809524</v>
       </c>
     </row>
     <row r="16">
@@ -1070,26 +1653,73 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.079119571683522</v>
+        <v>2698.412698412698</v>
       </c>
       <c r="D16" t="n">
-        <v>12.67634169357579</v>
+        <v>247.4904806840987</v>
       </c>
       <c r="E16" t="n">
-        <v>11.74012765651796</v>
+        <v>229.2120161510649</v>
       </c>
       <c r="F16" t="n">
         <v>1.079744791917834</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5536065726636294</v>
+        <v>0.5536065726636293</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.6796875</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7.436755952380952</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.640531994047618</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.572172619047619</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7.436755952380952</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.936011904761903</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.886904761904762</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.877604166666667</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.6796875</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="n">
+        <v>6.498139880952381</v>
       </c>
     </row>
     <row r="17">
@@ -1100,26 +1730,73 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.997025580011898</v>
+        <v>2667.120181405895</v>
       </c>
       <c r="D17" t="n">
-        <v>12.68817781529776</v>
+        <v>247.721566870099</v>
       </c>
       <c r="E17" t="n">
-        <v>11.65440279972263</v>
+        <v>227.538340375537</v>
       </c>
       <c r="F17" t="n">
         <v>1.088702530137343</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5461661912890234</v>
+        <v>0.5461661912890236</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.573660714285714</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7.427455357142857</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.770275297619047</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.605654761904762</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7.427455357142857</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6.071800595238095</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.404017857142857</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.825520833333333</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.573660714285714</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="n">
+        <v>4.812127976190476</v>
       </c>
     </row>
     <row r="18">
@@ -1130,26 +1807,73 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.913146936347412</v>
+        <v>2635.147392290249</v>
       </c>
       <c r="D18" t="n">
-        <v>12.68817780948267</v>
+        <v>247.7215667565663</v>
       </c>
       <c r="E18" t="n">
-        <v>11.46173220436748</v>
+        <v>223.776676370984</v>
       </c>
       <c r="F18" t="n">
         <v>1.107003512492454</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5396188841002802</v>
+        <v>0.5396188841002801</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.659970238095238</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7.217261904761904</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.765159970238095</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.720982142857142</v>
+      </c>
+      <c r="T18" t="n">
+        <v>7.217261904761904</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5.890252976190475</v>
+      </c>
+      <c r="V18" t="n">
+        <v>3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.204985119047619</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.805059523809524</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.659970238095238</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="n">
+        <v>4.462218915343914</v>
       </c>
     </row>
     <row r="19">
@@ -1160,26 +1884,73 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6.852766210588936</v>
+        <v>2612.131519274376</v>
       </c>
       <c r="D19" t="n">
-        <v>12.60490429982906</v>
+        <v>246.0957506157103</v>
       </c>
       <c r="E19" t="n">
-        <v>11.28334906043076</v>
+        <v>220.2939578465053</v>
       </c>
       <c r="F19" t="n">
-        <v>1.11712437790592</v>
+        <v>1.117124377905921</v>
       </c>
       <c r="G19" t="n">
         <v>0.541996739819619</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.408854166666667</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7.472098214285714</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.58403087797619</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.674479166666666</v>
+      </c>
+      <c r="T19" t="n">
+        <v>7.472098214285714</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5.733630952380952</v>
+      </c>
+      <c r="V19" t="n">
+        <v>3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.981770833333333</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.613467261904762</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.408854166666667</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="n">
+        <v>7.746775793650793</v>
       </c>
     </row>
     <row r="20">
@@ -1190,26 +1961,73 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.759666864961333</v>
+        <v>2576.643990929705</v>
       </c>
       <c r="D20" t="n">
-        <v>12.36691995074109</v>
+        <v>241.4493895144689</v>
       </c>
       <c r="E20" t="n">
-        <v>11.10843267091891</v>
+        <v>216.8789235750834</v>
       </c>
       <c r="F20" t="n">
         <v>1.113291165108901</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5554079065824037</v>
+        <v>0.5554079065824038</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.188616071428571</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8.3203125</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.213402157738095</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.172247023809524</v>
+      </c>
+      <c r="T20" t="n">
+        <v>8.3203125</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5.977027529761905</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.188616071428571</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.755580357142857</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.449776785714286</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="n">
+        <v>6.001426091269841</v>
       </c>
     </row>
     <row r="21">
@@ -1220,26 +2038,73 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.759666864961333</v>
+        <v>2576.643990929705</v>
       </c>
       <c r="D21" t="n">
-        <v>12.36691995074109</v>
+        <v>241.4493895144689</v>
       </c>
       <c r="E21" t="n">
-        <v>11.10843267091891</v>
+        <v>216.8789235750834</v>
       </c>
       <c r="F21" t="n">
         <v>1.113291165108901</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5554079065824037</v>
+        <v>0.5554079065824038</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.188616071428571</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8.3203125</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.213402157738095</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.172247023809524</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8.3203125</v>
+      </c>
+      <c r="U21" t="n">
+        <v>5.977027529761905</v>
+      </c>
+      <c r="V21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.188616071428571</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.755580357142857</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.449776785714286</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="22">
@@ -1249,7 +2114,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="n">
+        <v>3.220982142857143</v>
       </c>
     </row>
     <row r="23">
@@ -1263,6 +2136,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="n">
+        <v>2.837425595238095</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1272,6 +2153,80 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AG24" s="2" t="n">
+        <v>2.011904761904762</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AG25" s="2" t="n">
+        <v>1.497891865079365</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AG26" s="2" t="n">
+        <v>3.479662698412698</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG27" s="2" t="n">
+        <v>2.433386479591837</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/31/Filled_2D_sections/sagittal/week31_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/31/Filled_2D_sections/sagittal/week31_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2232,4 +2438,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week31_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2732.528344671202</v>
+      </c>
+      <c r="D10" t="n">
+        <v>87.31310962845967</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2576.643990929705</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2870.294784580499</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>260.7937958893321</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15.66129112507274</v>
+      </c>
+      <c r="E11" t="n">
+        <v>241.4493895144689</v>
+      </c>
+      <c r="F11" t="n">
+        <v>289.4068549928211</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.12647294165192</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.05151524690683276</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.073836703326018</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.235341834273857</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5091507094526134</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.05329476452470242</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4083942641036674</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.560542605584105</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0145.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0147.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>9</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0152.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>9</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>9</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0153.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0154.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>9</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>9</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0155.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0156.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0157.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>9</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0158.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0159.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0160.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0161.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0162.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0163.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>8</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0163.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.9679060415469872</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.7591546545162482</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.852452144420584</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.446411166701189</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>11</v>
+      </c>
+      <c r="C48" t="n">
+        <v>15.6255073051948</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.516744559640314</v>
+      </c>
+      <c r="E48" t="n">
+        <v>13.05245535714286</v>
+      </c>
+      <c r="F48" t="n">
+        <v>17.54650297619047</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>56</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.491217580782313</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.693585144276645</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.172247023809524</v>
+      </c>
+      <c r="F49" t="n">
+        <v>11.64248511904762</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>95</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.467555607769424</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.731268397489454</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.188616071428571</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.066220238095238</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>